--- a/InputData/trans/AVLRaPTC/Annual Vehicle Licensing Registration and Property Tax Costs.xlsx
+++ b/InputData/trans/AVLRaPTC/Annual Vehicle Licensing Registration and Property Tax Costs.xlsx
@@ -819,4 +819,175 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32C974C1-A27E-4939-B3A1-C02AFB5993F8}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DEA72DF-C5E6-488B-9DB3-5B17317C19E2}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{297D8F00-D632-4504-B6E1-49A8C6BB421E}"/>
 </file>
--- a/InputData/trans/AVLRaPTC/Annual Vehicle Licensing Registration and Property Tax Costs.xlsx
+++ b/InputData/trans/AVLRaPTC/Annual Vehicle Licensing Registration and Property Tax Costs.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeff Rissman\CodeRepositories\eps-us\InputData\trans\AVLRaPTC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\trans\AVLRaPTC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D32A06-ED03-485E-BDB4-2BF12EEC6254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E6BD79-B169-4D88-B996-8934398C56E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33735" yWindow="675" windowWidth="21600" windowHeight="22305" xr2:uid="{AF599D04-C13D-45D7-BEF0-770B4B16FC27}"/>
+    <workbookView xWindow="-28485" yWindow="390" windowWidth="21600" windowHeight="12525" xr2:uid="{AF599D04-C13D-45D7-BEF0-770B4B16FC27}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="AVLRaPTC" sheetId="2" r:id="rId2"/>
+    <sheet name="EV Fees" sheetId="6" r:id="rId2"/>
+    <sheet name="VSbS-passenger" sheetId="7" r:id="rId3"/>
+    <sheet name="AVLRaPTC-psgr" sheetId="2" r:id="rId4"/>
+    <sheet name="AVLRaPTC-frgt" sheetId="9" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,8 +37,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="157">
   <si>
     <t>Sources:</t>
   </si>
@@ -103,12 +128,6 @@
     <t>2012 USD/year</t>
   </si>
   <si>
-    <t>passenger</t>
-  </si>
-  <si>
-    <t>freight</t>
-  </si>
-  <si>
     <t>LDVs</t>
   </si>
   <si>
@@ -140,6 +159,378 @@
   </si>
   <si>
     <t>AVLRaPTC Annual Vehicle Licensing Registration and Property Tax Costs</t>
+  </si>
+  <si>
+    <t>Electric Vehicles: EV Taxes by State, 2025 | Tax Foundation</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>EV Purchase Tax Credit</t>
+  </si>
+  <si>
+    <t>EV Annual Registration Fee</t>
+  </si>
+  <si>
+    <t>Hybrid Annual Registration Fee</t>
+  </si>
+  <si>
+    <t>Alabama</t>
+  </si>
+  <si>
+    <t>Alaska</t>
+  </si>
+  <si>
+    <t>Arizona</t>
+  </si>
+  <si>
+    <t>Arkansas</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>0 (b)</t>
+  </si>
+  <si>
+    <t>Colorado</t>
+  </si>
+  <si>
+    <t>Connecticut</t>
+  </si>
+  <si>
+    <t>750-5,000</t>
+  </si>
+  <si>
+    <t>Delaware</t>
+  </si>
+  <si>
+    <t>1,000-2,500 (c)</t>
+  </si>
+  <si>
+    <t>Florida</t>
+  </si>
+  <si>
+    <t>0 (d)</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>Hawaii</t>
+  </si>
+  <si>
+    <t>Idaho</t>
+  </si>
+  <si>
+    <t>Illinois</t>
+  </si>
+  <si>
+    <t>4,000 (e)</t>
+  </si>
+  <si>
+    <t>Indiana</t>
+  </si>
+  <si>
+    <t>Iowa</t>
+  </si>
+  <si>
+    <t>Kansas</t>
+  </si>
+  <si>
+    <t>Up to 4000</t>
+  </si>
+  <si>
+    <t>Kentucky</t>
+  </si>
+  <si>
+    <t>Louisiana</t>
+  </si>
+  <si>
+    <t>Maine</t>
+  </si>
+  <si>
+    <t>Up to 7,500 (f)</t>
+  </si>
+  <si>
+    <t>Maryland</t>
+  </si>
+  <si>
+    <t>3,000 (g)</t>
+  </si>
+  <si>
+    <t>Massachusetts</t>
+  </si>
+  <si>
+    <t>Up to 3,500</t>
+  </si>
+  <si>
+    <t>Michigan</t>
+  </si>
+  <si>
+    <t>Minnesota</t>
+  </si>
+  <si>
+    <t>Mississippi</t>
+  </si>
+  <si>
+    <t>Missouri</t>
+  </si>
+  <si>
+    <t>Montana</t>
+  </si>
+  <si>
+    <t>Nebraska</t>
+  </si>
+  <si>
+    <t>Nevada</t>
+  </si>
+  <si>
+    <t>New Hampshire</t>
+  </si>
+  <si>
+    <t>New Jersey</t>
+  </si>
+  <si>
+    <t>Up to 4,000 (b)(h)</t>
+  </si>
+  <si>
+    <t>New Mexico</t>
+  </si>
+  <si>
+    <t>Up to 3000</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>Up to 2,000</t>
+  </si>
+  <si>
+    <t>North Carolina</t>
+  </si>
+  <si>
+    <t>North Dakota</t>
+  </si>
+  <si>
+    <t>Ohio</t>
+  </si>
+  <si>
+    <t>Oklahoma</t>
+  </si>
+  <si>
+    <t>Up to 5,500</t>
+  </si>
+  <si>
+    <t>Oregon</t>
+  </si>
+  <si>
+    <t>Up to 7,500 (f) (h)</t>
+  </si>
+  <si>
+    <t>Pennsylvania</t>
+  </si>
+  <si>
+    <t>Up to 3,000 (f) (k)</t>
+  </si>
+  <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>Up to 1,500</t>
+  </si>
+  <si>
+    <t>South Carolina</t>
+  </si>
+  <si>
+    <t>South Dakota</t>
+  </si>
+  <si>
+    <t>Tennessee</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>Utah</t>
+  </si>
+  <si>
+    <t>Vermont</t>
+  </si>
+  <si>
+    <t>Up to 5,000 (c)</t>
+  </si>
+  <si>
+    <t>Virginia</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>0 (e)</t>
+  </si>
+  <si>
+    <t>West Virginia</t>
+  </si>
+  <si>
+    <t>Wisconsin</t>
+  </si>
+  <si>
+    <t>Wyoming</t>
+  </si>
+  <si>
+    <t>EV Taxes by State, 2025</t>
+  </si>
+  <si>
+    <t>Tax Foundation</t>
+  </si>
+  <si>
+    <t>Electric Vehicle Taxes by State, 2025</t>
+  </si>
+  <si>
+    <t>https://taxfoundation.org/data/all/state/electric-vehicle-ev-taxes/</t>
+  </si>
+  <si>
+    <t>Unit: dimensionless (share of vehicles)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alaska </t>
+  </si>
+  <si>
+    <t xml:space="preserve">California </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colorado </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delaware </t>
+  </si>
+  <si>
+    <t>District of Columbia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Florida </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Georgia </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Illinois </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indiana </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iowa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maine </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minnesota </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mississippi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montana </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nevada </t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Jersey </t>
+  </si>
+  <si>
+    <t xml:space="preserve">New York </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oklahoma  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oregon </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhode Island </t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Dakota </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tennessee </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Texas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Washington </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wisconsin </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wyoming </t>
+  </si>
+  <si>
+    <t>subregion52</t>
+  </si>
+  <si>
+    <t>subregion53</t>
+  </si>
+  <si>
+    <t>subregion54</t>
+  </si>
+  <si>
+    <t>subregion55</t>
+  </si>
+  <si>
+    <t>subregion56</t>
+  </si>
+  <si>
+    <t>subregion57</t>
+  </si>
+  <si>
+    <t>subregion58</t>
+  </si>
+  <si>
+    <t>subregion59</t>
+  </si>
+  <si>
+    <t>subregion60</t>
+  </si>
+  <si>
+    <t>battery electric vehicle</t>
+  </si>
+  <si>
+    <t>natural gas vehicle</t>
+  </si>
+  <si>
+    <t>gasoline vehicle</t>
+  </si>
+  <si>
+    <t>diesel vehicle</t>
+  </si>
+  <si>
+    <t>plugin hybrid vehicle</t>
+  </si>
+  <si>
+    <t>LPG vehicle</t>
+  </si>
+  <si>
+    <t>hydrogen vehicle</t>
+  </si>
+  <si>
+    <t>Sales Share</t>
+  </si>
+  <si>
+    <t>psgr-LDV</t>
+  </si>
+  <si>
+    <t>Some states have higher EV registration fees to make up from lost revenue from gas taxes that don't affect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEVs and make less off PHEVs. We add an incremental EV registration fee weighted by U.S. state. </t>
   </si>
 </sst>
 </file>
@@ -149,7 +540,7 @@
   <numFmts count="1">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -172,6 +563,20 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -209,11 +614,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -225,15 +631,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{B6C0E403-779D-4556-BCCA-F20487B26FAF}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -249,9 +664,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -289,7 +704,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -395,7 +810,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -537,7 +952,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -545,7 +960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FC3CD7F-A224-4C3A-9A5E-D38F07B136AE}">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="61.42578125" customWidth="1"/>
@@ -553,7 +968,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -610,105 +1025,140 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="B15" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="3">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="5">
-        <v>753</v>
-      </c>
-      <c r="B17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>16</v>
+      <c r="A23" s="5">
+        <v>753</v>
+      </c>
+      <c r="B23" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="B36" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="8">
+        <v>2</v>
+      </c>
+      <c r="B37" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="8">
+        <v>1</v>
+      </c>
+      <c r="B38" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="B30" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="9">
-        <v>2</v>
-      </c>
-      <c r="B31" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="9">
-        <v>1</v>
-      </c>
-      <c r="B32" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45">
         <v>0.89800000000000002</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B45" t="s">
         <v>20</v>
       </c>
     </row>
@@ -723,96 +1173,2372 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D0F4B8D-70F0-48E9-8C0A-87C272523328}">
-  <sheetPr>
-    <tabColor theme="4" tint="-0.249977111117893"/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7608B96-D6A9-4327-9F51-87B18DC27DF1}">
+  <dimension ref="A1:E53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.140625" customWidth="1"/>
-    <col min="2" max="3" width="12.28515625" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" style="11" customWidth="1"/>
+    <col min="2" max="2" width="29.7109375" style="11" customWidth="1"/>
+    <col min="3" max="3" width="35.140625" style="11" customWidth="1"/>
+    <col min="4" max="4" width="40.42578125" style="11" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="7" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="16" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="13">
+        <v>0</v>
+      </c>
+      <c r="C3" s="13">
+        <v>203</v>
+      </c>
+      <c r="D3" s="13">
+        <v>103</v>
+      </c>
+      <c r="E3" s="11" cm="1">
+        <f t="array" ref="E3">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A3),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>1.9359587000000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="13">
+        <v>0</v>
+      </c>
+      <c r="C4" s="13">
+        <v>0</v>
+      </c>
+      <c r="D4" s="13">
+        <v>0</v>
+      </c>
+      <c r="E4" s="11" cm="1">
+        <f t="array" ref="E4">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A4),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>1.6278449999999999E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="13">
+        <v>0</v>
+      </c>
+      <c r="C5" s="13">
+        <v>0</v>
+      </c>
+      <c r="D5" s="13">
+        <v>0</v>
+      </c>
+      <c r="E5" s="11" cm="1">
+        <f t="array" ref="E5">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A5),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>2.2923013999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="13">
+        <v>0</v>
+      </c>
+      <c r="C6" s="13">
+        <v>200</v>
+      </c>
+      <c r="D6" s="11">
+        <v>100</v>
+      </c>
+      <c r="E6" s="11" cm="1">
+        <f t="array" ref="E6">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A6),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>8.2982309999999997E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="13">
+        <v>118</v>
+      </c>
+      <c r="D7" s="13">
+        <v>0</v>
+      </c>
+      <c r="E7" s="11" cm="1">
+        <f t="array" ref="E7">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A7),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>0.135077372</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="13">
+        <v>3500</v>
+      </c>
+      <c r="C8" s="14">
+        <v>60.05</v>
+      </c>
+      <c r="D8" s="13">
+        <v>0</v>
+      </c>
+      <c r="E8" s="11" cm="1">
+        <f t="array" ref="E8">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A8),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>1.5589702E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="13">
+        <v>0</v>
+      </c>
+      <c r="D9" s="13">
+        <v>0</v>
+      </c>
+      <c r="E9" s="11" cm="1">
+        <f t="array" ref="E9">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A9),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>1.1520117E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="13">
+        <v>0</v>
+      </c>
+      <c r="D10" s="13">
+        <v>0</v>
+      </c>
+      <c r="E10" s="11" cm="1">
+        <f t="array" ref="E10">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A10),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>3.9559979999999996E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="13">
+        <v>0</v>
+      </c>
+      <c r="D11" s="13">
+        <v>0</v>
+      </c>
+      <c r="E11" s="11" cm="1">
+        <f t="array" ref="E11">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A11),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>7.4585348999999995E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="13">
+        <v>0</v>
+      </c>
+      <c r="C12" s="14">
+        <v>234.97</v>
+      </c>
+      <c r="D12" s="13">
+        <v>0</v>
+      </c>
+      <c r="E12" s="11" cm="1">
+        <f t="array" ref="E12">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A12),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>3.3246882999999998E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="13">
+        <v>0</v>
+      </c>
+      <c r="C13" s="13">
+        <v>50</v>
+      </c>
+      <c r="D13" s="13">
+        <v>0</v>
+      </c>
+      <c r="E13" s="11" cm="1">
+        <f t="array" ref="E13">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A13),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>4.517788E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="13">
+        <v>0</v>
+      </c>
+      <c r="C14" s="13">
+        <v>140</v>
+      </c>
+      <c r="D14" s="13">
+        <v>75</v>
+      </c>
+      <c r="E14" s="11" cm="1">
+        <f t="array" ref="E14">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A14),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>5.5962360000000001E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="13">
+        <v>100</v>
+      </c>
+      <c r="D15" s="13">
+        <v>0</v>
+      </c>
+      <c r="E15" s="11" cm="1">
+        <f t="array" ref="E15">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A15),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>3.9583803000000001E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="13">
+        <v>0</v>
+      </c>
+      <c r="C16" s="13">
+        <v>230</v>
+      </c>
+      <c r="D16" s="13">
+        <v>77</v>
+      </c>
+      <c r="E16" s="11" cm="1">
+        <f t="array" ref="E16">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A16),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>2.0200142000000001E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="13">
+        <v>0</v>
+      </c>
+      <c r="C17" s="13">
+        <v>130</v>
+      </c>
+      <c r="D17" s="11">
+        <v>65</v>
+      </c>
+      <c r="E17" s="11" cm="1">
+        <f t="array" ref="E17">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A17),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>1.106908E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="13">
+        <v>165</v>
+      </c>
+      <c r="D18" s="13">
+        <v>70</v>
+      </c>
+      <c r="E18" s="11" cm="1">
+        <f t="array" ref="E18">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A18),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>8.4565600000000001E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="13">
+        <v>0</v>
+      </c>
+      <c r="C19" s="13">
+        <v>120</v>
+      </c>
+      <c r="D19" s="13">
+        <v>60</v>
+      </c>
+      <c r="E19" s="11" cm="1">
+        <f t="array" ref="E19">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A19),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>1.5641721000000001E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="13">
+        <v>0</v>
+      </c>
+      <c r="C20" s="13">
+        <v>110</v>
+      </c>
+      <c r="D20" s="11">
+        <v>60</v>
+      </c>
+      <c r="E20" s="11" cm="1">
+        <f t="array" ref="E20">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A20),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>1.2514265E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="13">
+        <v>0</v>
+      </c>
+      <c r="D21" s="13">
+        <v>0</v>
+      </c>
+      <c r="E21" s="11" cm="1">
+        <f t="array" ref="E21">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A21),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>3.3868639999999998E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="13">
+        <v>125</v>
+      </c>
+      <c r="D22" s="11">
+        <v>100</v>
+      </c>
+      <c r="E22" s="11" cm="1">
+        <f t="array" ref="E22">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A22),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>1.7344821E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="13">
+        <v>0</v>
+      </c>
+      <c r="D23" s="13">
+        <v>0</v>
+      </c>
+      <c r="E23" s="11" cm="1">
+        <f t="array" ref="E23">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A23),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>1.9055189E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" s="13">
+        <v>0</v>
+      </c>
+      <c r="C24" s="13">
+        <v>160</v>
+      </c>
+      <c r="D24" s="11">
+        <v>60</v>
+      </c>
+      <c r="E24" s="11" cm="1">
+        <f t="array" ref="E24">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A24),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>2.5602285999999998E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" s="13">
+        <v>0</v>
+      </c>
+      <c r="C25" s="13">
+        <v>75</v>
+      </c>
+      <c r="D25" s="13">
+        <v>0</v>
+      </c>
+      <c r="E25" s="11" cm="1">
+        <f t="array" ref="E25">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A25),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>1.7517332E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="13">
+        <v>150</v>
+      </c>
+      <c r="D26" s="13">
+        <v>75</v>
+      </c>
+      <c r="E26" s="11" cm="1">
+        <f t="array" ref="E26">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A26),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>7.4991459999999999E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27" s="13">
+        <v>0</v>
+      </c>
+      <c r="C27" s="13">
+        <v>135</v>
+      </c>
+      <c r="D27" s="11">
+        <v>67.5</v>
+      </c>
+      <c r="E27" s="11" cm="1">
+        <f t="array" ref="E27">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A27),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>1.8941079E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B28" s="13">
+        <v>0</v>
+      </c>
+      <c r="C28" s="11">
+        <f>AVERAGE(130,190)</f>
+        <v>160</v>
+      </c>
+      <c r="D28" s="11">
+        <v>85</v>
+      </c>
+      <c r="E28" s="11" cm="1">
+        <f t="array" ref="E28">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A28),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>4.3665730000000003E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="13">
+        <v>0</v>
+      </c>
+      <c r="C29" s="13">
+        <v>150</v>
+      </c>
+      <c r="D29" s="13">
+        <v>75</v>
+      </c>
+      <c r="E29" s="11" cm="1">
+        <f t="array" ref="E29">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A29),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>5.9438360000000001E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" s="13">
+        <v>0</v>
+      </c>
+      <c r="D30" s="13">
+        <v>0</v>
+      </c>
+      <c r="E30" s="11" cm="1">
+        <f t="array" ref="E30">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A30),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>9.7731490000000001E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" s="13">
+        <v>100</v>
+      </c>
+      <c r="D31" s="13">
+        <v>50</v>
+      </c>
+      <c r="E31" s="11" cm="1">
+        <f t="array" ref="E31">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A31),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>4.3831620000000003E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="13">
+        <v>260</v>
+      </c>
+      <c r="D32" s="13">
+        <v>0</v>
+      </c>
+      <c r="E32" s="11" cm="1">
+        <f t="array" ref="E32">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A32),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>2.4170046000000001E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" s="13">
+        <v>0</v>
+      </c>
+      <c r="D33" s="13">
+        <v>0</v>
+      </c>
+      <c r="E33" s="11" cm="1">
+        <f t="array" ref="E33">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A33),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>5.9347810000000001E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" s="13">
+        <v>0</v>
+      </c>
+      <c r="D34" s="13">
+        <v>0</v>
+      </c>
+      <c r="E34" s="11" cm="1">
+        <f t="array" ref="E34">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A34),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>4.0260008E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35" s="13">
+        <v>0</v>
+      </c>
+      <c r="C35" s="11">
+        <v>214.5</v>
+      </c>
+      <c r="D35" s="14">
+        <v>107.25</v>
+      </c>
+      <c r="E35" s="11" cm="1">
+        <f t="array" ref="E35">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A35),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>3.2324727999999997E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="13">
+        <v>0</v>
+      </c>
+      <c r="C36" s="13">
+        <v>120</v>
+      </c>
+      <c r="D36" s="13">
+        <v>50</v>
+      </c>
+      <c r="E36" s="11" cm="1">
+        <f t="array" ref="E36">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A36),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>2.051204E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B37" s="13">
+        <v>0</v>
+      </c>
+      <c r="C37" s="13">
+        <v>200</v>
+      </c>
+      <c r="D37" s="11">
+        <v>150</v>
+      </c>
+      <c r="E37" s="11" cm="1">
+        <f t="array" ref="E37">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A37),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>4.0403584999999999E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38" s="13">
+        <v>110</v>
+      </c>
+      <c r="D38" s="11">
+        <v>82</v>
+      </c>
+      <c r="E38" s="11" cm="1">
+        <f t="array" ref="E38">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A38),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>1.1640695E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" s="11">
+        <v>115</v>
+      </c>
+      <c r="D39" s="11">
+        <v>35</v>
+      </c>
+      <c r="E39" s="11" cm="1">
+        <f t="array" ref="E39">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A39),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>1.3704701999999999E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" s="13">
+        <v>200</v>
+      </c>
+      <c r="D40" s="13">
+        <v>50</v>
+      </c>
+      <c r="E40" s="11" cm="1">
+        <f t="array" ref="E40">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A40),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>3.8462009999999998E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" s="13">
+        <v>200</v>
+      </c>
+      <c r="D41" s="11">
+        <v>100</v>
+      </c>
+      <c r="E41" s="11" cm="1">
+        <f t="array" ref="E41">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A41),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>3.6311970000000001E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" s="13">
+        <v>0</v>
+      </c>
+      <c r="C42" s="11">
+        <v>60</v>
+      </c>
+      <c r="D42" s="11">
+        <v>30</v>
+      </c>
+      <c r="E42" s="11" cm="1">
+        <f t="array" ref="E42">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A42),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>1.6810225000000002E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43" s="13">
+        <v>0</v>
+      </c>
+      <c r="C43" s="13">
+        <v>50</v>
+      </c>
+      <c r="D43" s="13">
+        <v>0</v>
+      </c>
+      <c r="E43" s="11" cm="1">
+        <f t="array" ref="E43">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A43),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>3.0912639999999998E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B44" s="13">
+        <v>0</v>
+      </c>
+      <c r="C44" s="13">
+        <v>200</v>
+      </c>
+      <c r="D44" s="13">
+        <v>100</v>
+      </c>
+      <c r="E44" s="11" cm="1">
+        <f t="array" ref="E44">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A44),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>2.0122945999999999E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45" s="13">
+        <v>0</v>
+      </c>
+      <c r="C45" s="11">
+        <v>200</v>
+      </c>
+      <c r="D45" s="13">
+        <v>0</v>
+      </c>
+      <c r="E45" s="11" cm="1">
+        <f t="array" ref="E45">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A45),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>7.6929994000000002E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B46" s="13">
+        <v>0</v>
+      </c>
+      <c r="C46" s="11">
+        <v>130.25</v>
+      </c>
+      <c r="D46" s="11">
+        <v>56.5</v>
+      </c>
+      <c r="E46" s="11" cm="1">
+        <f t="array" ref="E46">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A46),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>8.5862979999999992E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C47" s="13">
+        <v>89</v>
+      </c>
+      <c r="D47" s="11">
+        <v>44.5</v>
+      </c>
+      <c r="E47" s="11" cm="1">
+        <f t="array" ref="E47">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A47),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>1.839601E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B48" s="15">
+        <v>2500</v>
+      </c>
+      <c r="C48" s="11">
+        <v>131.88</v>
+      </c>
+      <c r="D48" s="11">
+        <v>0</v>
+      </c>
+      <c r="E48" s="11" cm="1">
+        <f t="array" ref="E48">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A48),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>2.9079233999999999E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C49" s="13">
+        <v>150</v>
+      </c>
+      <c r="D49" s="11">
+        <v>75</v>
+      </c>
+      <c r="E49" s="11" cm="1">
+        <f t="array" ref="E49">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A49),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>2.6635868E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B50" s="13">
+        <v>0</v>
+      </c>
+      <c r="C50" s="13">
+        <v>200</v>
+      </c>
+      <c r="D50" s="13">
+        <v>100</v>
+      </c>
+      <c r="E50" s="11" cm="1">
+        <f t="array" ref="E50">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A50),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>4.8381750000000001E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="B51" s="13">
+        <v>0</v>
+      </c>
+      <c r="C51" s="13">
+        <v>175</v>
+      </c>
+      <c r="D51" s="11">
+        <v>75</v>
+      </c>
+      <c r="E51" s="11" cm="1">
+        <f t="array" ref="E51">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A51),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>1.8086189999999999E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B52" s="13">
+        <v>0</v>
+      </c>
+      <c r="C52" s="13">
+        <v>200</v>
+      </c>
+      <c r="D52" s="13">
+        <v>0</v>
+      </c>
+      <c r="E52" s="11" cm="1">
+        <f t="array" ref="E52">INDEX('VSbS-passenger'!B$2:B$52,MATCH(TRIM('EV Fees'!$A52),TRIM('VSbS-passenger'!$A$2:$A$52),0))</f>
+        <v>1.819864E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C53" s="14">
+        <f>SUMPRODUCT(C$3:C$52,$E$3:$E$52)</f>
+        <v>126.27012827002999</v>
+      </c>
+      <c r="D53" s="14">
+        <f>SUMPRODUCT(D$3:D$52,$E$3:$E$52)</f>
+        <v>34.219388372000004</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E12DFAA1-EC90-44F0-834A-84976102E1A1}">
+  <dimension ref="A1:G61"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="36.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="D1" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="8">
-        <f>About!A17*About!$A$36</f>
-        <v>676.19399999999996</v>
-      </c>
-      <c r="C2" s="8">
-        <f>$B$2*About!$A$32</f>
-        <v>676.19399999999996</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="E1" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="8">
-        <f>$B$2*About!$A$31</f>
-        <v>1352.3879999999999</v>
-      </c>
-      <c r="C3" s="8">
-        <f>$B$2*About!$A$31</f>
-        <v>1352.3879999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="F1" t="s">
         <v>26</v>
       </c>
+      <c r="G1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2">
+        <v>1.9359587000000001E-2</v>
+      </c>
+      <c r="C2">
+        <v>5.5878519999999999E-3</v>
+      </c>
+      <c r="D2">
+        <v>1.9282655999999999E-2</v>
+      </c>
+      <c r="E2">
+        <v>1.9282655999999999E-2</v>
+      </c>
+      <c r="F2">
+        <v>1.9282655999999999E-2</v>
+      </c>
+      <c r="G2">
+        <v>1.3796717999999999E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B3">
+        <v>1.6278449999999999E-3</v>
+      </c>
+      <c r="C3">
+        <v>8.5645960000000007E-3</v>
+      </c>
+      <c r="D3">
+        <v>2.8734609999999999E-3</v>
+      </c>
+      <c r="E3">
+        <v>2.8734609999999999E-3</v>
+      </c>
+      <c r="F3">
+        <v>2.8734609999999999E-3</v>
+      </c>
+      <c r="G3">
+        <v>3.2157240000000001E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
       <c r="B4">
-        <v>0</v>
+        <v>2.2923013999999999E-2</v>
       </c>
       <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>27</v>
+        <v>8.4314569999999998E-3</v>
+      </c>
+      <c r="D4">
+        <v>2.1940886E-2</v>
+      </c>
+      <c r="E4">
+        <v>2.1940886E-2</v>
+      </c>
+      <c r="F4">
+        <v>2.1940886E-2</v>
+      </c>
+      <c r="G4">
+        <v>1.4537939999999999E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>41</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>8.2982309999999997E-3</v>
       </c>
       <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>28</v>
+        <v>1.1966588E-2</v>
+      </c>
+      <c r="D5">
+        <v>1.0559004E-2</v>
+      </c>
+      <c r="E5">
+        <v>1.0559004E-2</v>
+      </c>
+      <c r="F5">
+        <v>1.0559004E-2</v>
+      </c>
+      <c r="G5">
+        <v>2.0388346000000002E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>112</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>0.135077372</v>
       </c>
       <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="8">
-        <f>$B$2*About!$A$30</f>
-        <v>338.09699999999998</v>
+        <v>0.100179936</v>
+      </c>
+      <c r="D6">
+        <v>0.110173217</v>
+      </c>
+      <c r="E6">
+        <v>0.110173217</v>
+      </c>
+      <c r="F6">
+        <v>0.110173217</v>
+      </c>
+      <c r="G6">
+        <v>9.4309654000000007E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7">
+        <v>1.5589702E-2</v>
       </c>
       <c r="C7">
+        <v>1.3631816E-2</v>
+      </c>
+      <c r="D7">
+        <v>1.9392718999999999E-2</v>
+      </c>
+      <c r="E7">
+        <v>1.9392718999999999E-2</v>
+      </c>
+      <c r="F7">
+        <v>1.9392718999999999E-2</v>
+      </c>
+      <c r="G7">
+        <v>2.1503721E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8">
+        <v>1.1520117E-2</v>
+      </c>
+      <c r="C8">
+        <v>1.1697330000000001E-2</v>
+      </c>
+      <c r="D8">
+        <v>1.0392956E-2</v>
+      </c>
+      <c r="E8">
+        <v>1.0392956E-2</v>
+      </c>
+      <c r="F8">
+        <v>1.0392956E-2</v>
+      </c>
+      <c r="G8">
+        <v>9.7199369999999997E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9">
+        <v>3.9559979999999996E-3</v>
+      </c>
+      <c r="C9">
+        <v>3.8341970000000001E-3</v>
+      </c>
+      <c r="D9">
+        <v>3.6465629999999998E-3</v>
+      </c>
+      <c r="E9">
+        <v>3.6465629999999998E-3</v>
+      </c>
+      <c r="F9">
+        <v>3.6465629999999998E-3</v>
+      </c>
+      <c r="G9">
+        <v>4.8306100000000002E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10">
+        <v>2.0002510000000002E-3</v>
+      </c>
+      <c r="C10">
+        <v>5.1000079999999996E-3</v>
+      </c>
+      <c r="D10">
+        <v>1.2922070000000001E-3</v>
+      </c>
+      <c r="E10">
+        <v>1.2922070000000001E-3</v>
+      </c>
+      <c r="F10">
+        <v>1.2922070000000001E-3</v>
+      </c>
+      <c r="G10">
+        <v>4.28307E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11">
+        <v>7.4585348999999995E-2</v>
+      </c>
+      <c r="C11">
+        <v>5.9786243000000003E-2</v>
+      </c>
+      <c r="D11">
+        <v>6.6921420999999995E-2</v>
+      </c>
+      <c r="E11">
+        <v>6.6921420999999995E-2</v>
+      </c>
+      <c r="F11">
+        <v>6.6921420999999995E-2</v>
+      </c>
+      <c r="G11">
+        <v>7.4455641000000003E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B12">
+        <v>3.3246882999999998E-2</v>
+      </c>
+      <c r="C12">
+        <v>3.6664815000000003E-2</v>
+      </c>
+      <c r="D12">
+        <v>3.2001349999999998E-2</v>
+      </c>
+      <c r="E12">
+        <v>3.2001349999999998E-2</v>
+      </c>
+      <c r="F12">
+        <v>3.2001349999999998E-2</v>
+      </c>
+      <c r="G12">
+        <v>2.4934379E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13">
+        <v>4.517788E-3</v>
+      </c>
+      <c r="C13">
+        <v>2.8664570000000002E-3</v>
+      </c>
+      <c r="D13">
+        <v>4.5120519999999999E-3</v>
+      </c>
+      <c r="E13">
+        <v>4.5120519999999999E-3</v>
+      </c>
+      <c r="F13">
+        <v>4.5120519999999999E-3</v>
+      </c>
+      <c r="G13">
+        <v>4.4403669999999998E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14">
+        <v>5.5962360000000001E-3</v>
+      </c>
+      <c r="C14">
+        <v>3.782531E-3</v>
+      </c>
+      <c r="D14">
+        <v>6.9502899999999996E-3</v>
+      </c>
+      <c r="E14">
+        <v>6.9502899999999996E-3</v>
+      </c>
+      <c r="F14">
+        <v>6.9502899999999996E-3</v>
+      </c>
+      <c r="G14">
+        <v>7.111432E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>118</v>
+      </c>
+      <c r="B15">
+        <v>3.9583803000000001E-2</v>
+      </c>
+      <c r="C15">
+        <v>3.2598123E-2</v>
+      </c>
+      <c r="D15">
+        <v>3.8373385000000003E-2</v>
+      </c>
+      <c r="E15">
+        <v>3.8373385000000003E-2</v>
+      </c>
+      <c r="F15">
+        <v>3.8373385000000003E-2</v>
+      </c>
+      <c r="G15">
+        <v>3.3659617000000003E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16">
+        <v>2.0200142000000001E-2</v>
+      </c>
+      <c r="C16">
+        <v>2.0735859999999998E-2</v>
+      </c>
+      <c r="D16">
+        <v>2.2470473000000001E-2</v>
+      </c>
+      <c r="E16">
+        <v>2.2470473000000001E-2</v>
+      </c>
+      <c r="F16">
+        <v>2.2470473000000001E-2</v>
+      </c>
+      <c r="G16">
+        <v>2.5194581000000001E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>120</v>
+      </c>
+      <c r="B17">
+        <v>1.106908E-2</v>
+      </c>
+      <c r="C17">
+        <v>9.1140409999999998E-3</v>
+      </c>
+      <c r="D17">
+        <v>1.3726141000000001E-2</v>
+      </c>
+      <c r="E17">
+        <v>1.3726141000000001E-2</v>
+      </c>
+      <c r="F17">
+        <v>1.3726141000000001E-2</v>
+      </c>
+      <c r="G17">
+        <v>2.3030833000000001E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18">
+        <v>8.4565600000000001E-3</v>
+      </c>
+      <c r="C18">
+        <v>6.5585729999999998E-3</v>
+      </c>
+      <c r="D18">
+        <v>9.4360929999999996E-3</v>
+      </c>
+      <c r="E18">
+        <v>9.4360929999999996E-3</v>
+      </c>
+      <c r="F18">
+        <v>9.4360929999999996E-3</v>
+      </c>
+      <c r="G18">
+        <v>1.0883943E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19">
+        <v>1.5641721000000001E-2</v>
+      </c>
+      <c r="C19">
+        <v>1.0917375E-2</v>
+      </c>
+      <c r="D19">
+        <v>1.6163360000000002E-2</v>
+      </c>
+      <c r="E19">
+        <v>1.6163360000000002E-2</v>
+      </c>
+      <c r="F19">
+        <v>1.6163360000000002E-2</v>
+      </c>
+      <c r="G19">
+        <v>1.1665989999999999E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20">
+        <v>1.2514265E-2</v>
+      </c>
+      <c r="C20">
+        <v>2.9889644E-2</v>
+      </c>
+      <c r="D20">
+        <v>1.3994269E-2</v>
+      </c>
+      <c r="E20">
+        <v>1.3994269E-2</v>
+      </c>
+      <c r="F20">
+        <v>1.3994269E-2</v>
+      </c>
+      <c r="G20">
+        <v>1.2186394999999999E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>121</v>
+      </c>
+      <c r="B21">
+        <v>3.3868639999999998E-3</v>
+      </c>
+      <c r="C21">
+        <v>4.5932860000000002E-3</v>
+      </c>
+      <c r="D21">
+        <v>4.0632560000000003E-3</v>
+      </c>
+      <c r="E21">
+        <v>4.0632560000000003E-3</v>
+      </c>
+      <c r="F21">
+        <v>4.0632560000000003E-3</v>
+      </c>
+      <c r="G21">
+        <v>4.6036690000000003E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22">
+        <v>1.7344821E-2</v>
+      </c>
+      <c r="C22">
+        <v>2.2395126000000001E-2</v>
+      </c>
+      <c r="D22">
+        <v>1.5263410999999999E-2</v>
+      </c>
+      <c r="E22">
+        <v>1.5263410999999999E-2</v>
+      </c>
+      <c r="F22">
+        <v>1.5263410999999999E-2</v>
+      </c>
+      <c r="G22">
+        <v>1.3514422E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23">
+        <v>1.9055189E-2</v>
+      </c>
+      <c r="C23">
+        <v>1.366361E-2</v>
+      </c>
+      <c r="D23">
+        <v>1.8254600999999999E-2</v>
+      </c>
+      <c r="E23">
+        <v>1.8254600999999999E-2</v>
+      </c>
+      <c r="F23">
+        <v>1.8254600999999999E-2</v>
+      </c>
+      <c r="G23">
+        <v>1.6585096000000001E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24">
+        <v>2.5602285999999998E-2</v>
+      </c>
+      <c r="C24">
+        <v>8.8845260000000002E-3</v>
+      </c>
+      <c r="D24">
+        <v>3.0637309000000001E-2</v>
+      </c>
+      <c r="E24">
+        <v>3.0637309000000001E-2</v>
+      </c>
+      <c r="F24">
+        <v>3.0637309000000001E-2</v>
+      </c>
+      <c r="G24">
+        <v>2.8515491E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25">
+        <v>1.7517332E-2</v>
+      </c>
+      <c r="C25">
+        <v>1.9068644999999999E-2</v>
+      </c>
+      <c r="D25">
+        <v>2.0625139000000001E-2</v>
+      </c>
+      <c r="E25">
+        <v>2.0625139000000001E-2</v>
+      </c>
+      <c r="F25">
+        <v>2.0625139000000001E-2</v>
+      </c>
+      <c r="G25">
+        <v>2.9294897E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26">
+        <v>7.4991459999999999E-3</v>
+      </c>
+      <c r="C26">
+        <v>7.3385270000000001E-3</v>
+      </c>
+      <c r="D26">
+        <v>7.4624000000000001E-3</v>
+      </c>
+      <c r="E26">
+        <v>7.4624000000000001E-3</v>
+      </c>
+      <c r="F26">
+        <v>7.4624000000000001E-3</v>
+      </c>
+      <c r="G26">
+        <v>3.6710480000000001E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>71</v>
+      </c>
+      <c r="B27">
+        <v>1.8941079E-2</v>
+      </c>
+      <c r="C27">
+        <v>3.3533075000000002E-2</v>
+      </c>
+      <c r="D27">
+        <v>2.0249198999999999E-2</v>
+      </c>
+      <c r="E27">
+        <v>2.0249198999999999E-2</v>
+      </c>
+      <c r="F27">
+        <v>2.0249198999999999E-2</v>
+      </c>
+      <c r="G27">
+        <v>1.5214201E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28">
+        <v>4.3665730000000003E-3</v>
+      </c>
+      <c r="C28">
+        <v>5.1616099999999996E-3</v>
+      </c>
+      <c r="D28">
+        <v>7.0766919999999999E-3</v>
+      </c>
+      <c r="E28">
+        <v>7.0766919999999999E-3</v>
+      </c>
+      <c r="F28">
+        <v>7.0766919999999999E-3</v>
+      </c>
+      <c r="G28">
+        <v>4.2647577999999998E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29">
+        <v>5.9438360000000001E-3</v>
+      </c>
+      <c r="C29">
+        <v>1.7177876000000002E-2</v>
+      </c>
+      <c r="D29">
+        <v>7.014368E-3</v>
+      </c>
+      <c r="E29">
+        <v>7.014368E-3</v>
+      </c>
+      <c r="F29">
+        <v>7.014368E-3</v>
+      </c>
+      <c r="G29">
+        <v>6.0485290000000004E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>125</v>
+      </c>
+      <c r="B30">
+        <v>9.7731490000000001E-3</v>
+      </c>
+      <c r="C30">
+        <v>3.1883739999999999E-3</v>
+      </c>
+      <c r="D30">
+        <v>9.2397050000000008E-3</v>
+      </c>
+      <c r="E30">
+        <v>9.2397050000000008E-3</v>
+      </c>
+      <c r="F30">
+        <v>9.2397050000000008E-3</v>
+      </c>
+      <c r="G30">
+        <v>8.3279100000000009E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31">
+        <v>4.3831620000000003E-3</v>
+      </c>
+      <c r="C31">
+        <v>3.060204E-3</v>
+      </c>
+      <c r="D31">
+        <v>4.9201519999999997E-3</v>
+      </c>
+      <c r="E31">
+        <v>4.9201519999999997E-3</v>
+      </c>
+      <c r="F31">
+        <v>4.9201519999999997E-3</v>
+      </c>
+      <c r="G31">
+        <v>9.4484479999999999E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>126</v>
+      </c>
+      <c r="B32">
+        <v>2.4170046000000001E-2</v>
+      </c>
+      <c r="C32">
+        <v>2.5791156999999999E-2</v>
+      </c>
+      <c r="D32">
+        <v>2.1768607999999998E-2</v>
+      </c>
+      <c r="E32">
+        <v>2.1768607999999998E-2</v>
+      </c>
+      <c r="F32">
+        <v>2.1768607999999998E-2</v>
+      </c>
+      <c r="G32">
+        <v>1.4574563E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33">
+        <v>5.9347810000000001E-3</v>
+      </c>
+      <c r="C33">
+        <v>9.7280690000000006E-3</v>
+      </c>
+      <c r="D33">
+        <v>6.4627240000000004E-3</v>
+      </c>
+      <c r="E33">
+        <v>6.4627240000000004E-3</v>
+      </c>
+      <c r="F33">
+        <v>6.4627240000000004E-3</v>
+      </c>
+      <c r="G33">
+        <v>6.597632E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34">
+        <v>4.0260008E-2</v>
+      </c>
+      <c r="C34">
+        <v>8.1156994999999996E-2</v>
+      </c>
+      <c r="D34">
+        <v>4.1044624000000002E-2</v>
+      </c>
+      <c r="E34">
+        <v>4.1044624000000002E-2</v>
+      </c>
+      <c r="F34">
+        <v>4.1044624000000002E-2</v>
+      </c>
+      <c r="G34">
+        <v>4.6183180999999997E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35">
+        <v>3.2324727999999997E-2</v>
+      </c>
+      <c r="C35">
+        <v>3.3117761000000003E-2</v>
+      </c>
+      <c r="D35">
+        <v>3.1674015E-2</v>
+      </c>
+      <c r="E35">
+        <v>3.1674015E-2</v>
+      </c>
+      <c r="F35">
+        <v>3.1674015E-2</v>
+      </c>
+      <c r="G35">
+        <v>2.2775793999999999E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36">
+        <v>2.051204E-3</v>
+      </c>
+      <c r="C36">
+        <v>3.6394560000000001E-3</v>
+      </c>
+      <c r="D36">
+        <v>3.258571E-3</v>
+      </c>
+      <c r="E36">
+        <v>3.258571E-3</v>
+      </c>
+      <c r="F36">
+        <v>3.258571E-3</v>
+      </c>
+      <c r="G36">
+        <v>4.3507909999999997E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>84</v>
+      </c>
+      <c r="B37">
+        <v>4.0403584999999999E-2</v>
+      </c>
+      <c r="C37">
+        <v>4.1215377999999997E-2</v>
+      </c>
+      <c r="D37">
+        <v>3.8390028E-2</v>
+      </c>
+      <c r="E37">
+        <v>3.8390028E-2</v>
+      </c>
+      <c r="F37">
+        <v>3.8390028E-2</v>
+      </c>
+      <c r="G37">
+        <v>4.5702522000000002E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>128</v>
+      </c>
+      <c r="B38">
+        <v>1.1640695E-2</v>
+      </c>
+      <c r="C38">
+        <v>2.8227399999999998E-3</v>
+      </c>
+      <c r="D38">
+        <v>1.3519638E-2</v>
+      </c>
+      <c r="E38">
+        <v>1.3519638E-2</v>
+      </c>
+      <c r="F38">
+        <v>1.3519638E-2</v>
+      </c>
+      <c r="G38">
+        <v>1.6077418999999999E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>129</v>
+      </c>
+      <c r="B39">
+        <v>1.3704701999999999E-2</v>
+      </c>
+      <c r="C39">
+        <v>1.7726328E-2</v>
+      </c>
+      <c r="D39">
+        <v>1.4843224E-2</v>
+      </c>
+      <c r="E39">
+        <v>1.4843224E-2</v>
+      </c>
+      <c r="F39">
+        <v>1.4843224E-2</v>
+      </c>
+      <c r="G39">
+        <v>1.484329E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40">
+        <v>3.8462009999999998E-2</v>
+      </c>
+      <c r="C40">
+        <v>5.4911776000000002E-2</v>
+      </c>
+      <c r="D40">
+        <v>3.8744740999999999E-2</v>
+      </c>
+      <c r="E40">
+        <v>3.8744740999999999E-2</v>
+      </c>
+      <c r="F40">
+        <v>3.8744740999999999E-2</v>
+      </c>
+      <c r="G40">
+        <v>4.3286136000000003E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>130</v>
+      </c>
+      <c r="B41">
+        <v>3.6311970000000001E-3</v>
+      </c>
+      <c r="C41">
+        <v>2.3031010000000001E-3</v>
+      </c>
+      <c r="D41">
+        <v>3.1409329999999998E-3</v>
+      </c>
+      <c r="E41">
+        <v>3.1409329999999998E-3</v>
+      </c>
+      <c r="F41">
+        <v>3.1409329999999998E-3</v>
+      </c>
+      <c r="G41">
+        <v>2.8346069999999998E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42">
+        <v>1.6810225000000002E-2</v>
+      </c>
+      <c r="C42">
+        <v>1.6360165999999999E-2</v>
+      </c>
+      <c r="D42">
+        <v>1.6531642999999999E-2</v>
+      </c>
+      <c r="E42">
+        <v>1.6531642999999999E-2</v>
+      </c>
+      <c r="F42">
+        <v>1.6531642999999999E-2</v>
+      </c>
+      <c r="G42">
+        <v>1.3750249000000001E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>131</v>
+      </c>
+      <c r="B43">
+        <v>3.0912639999999998E-3</v>
+      </c>
+      <c r="C43">
+        <v>2.6518449999999999E-3</v>
+      </c>
+      <c r="D43">
+        <v>4.6909020000000003E-3</v>
+      </c>
+      <c r="E43">
+        <v>4.6909020000000003E-3</v>
+      </c>
+      <c r="F43">
+        <v>4.6909020000000003E-3</v>
+      </c>
+      <c r="G43">
+        <v>1.5581991E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>132</v>
+      </c>
+      <c r="B44">
+        <v>2.0122945999999999E-2</v>
+      </c>
+      <c r="C44">
+        <v>2.9370005000000001E-2</v>
+      </c>
+      <c r="D44">
+        <v>2.1221791E-2</v>
+      </c>
+      <c r="E44">
+        <v>2.1221791E-2</v>
+      </c>
+      <c r="F44">
+        <v>2.1221791E-2</v>
+      </c>
+      <c r="G44">
+        <v>2.1285664999999999E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>133</v>
+      </c>
+      <c r="B45">
+        <v>7.6929994000000002E-2</v>
+      </c>
+      <c r="C45">
+        <v>7.0475097E-2</v>
+      </c>
+      <c r="D45">
+        <v>8.1255579999999994E-2</v>
+      </c>
+      <c r="E45">
+        <v>8.1255579999999994E-2</v>
+      </c>
+      <c r="F45">
+        <v>8.1255579999999994E-2</v>
+      </c>
+      <c r="G45">
+        <v>3.9420566999999997E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>97</v>
+      </c>
+      <c r="B46">
+        <v>8.5862979999999992E-3</v>
+      </c>
+      <c r="C46">
+        <v>6.3797300000000001E-3</v>
+      </c>
+      <c r="D46">
+        <v>8.9868980000000001E-3</v>
+      </c>
+      <c r="E46">
+        <v>8.9868980000000001E-3</v>
+      </c>
+      <c r="F46">
+        <v>8.9868980000000001E-3</v>
+      </c>
+      <c r="G46">
+        <v>1.4880153E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>98</v>
+      </c>
+      <c r="B47">
+        <v>1.839601E-3</v>
+      </c>
+      <c r="C47">
+        <v>1.0720650000000001E-3</v>
+      </c>
+      <c r="D47">
+        <v>2.203193E-3</v>
+      </c>
+      <c r="E47">
+        <v>2.203193E-3</v>
+      </c>
+      <c r="F47">
+        <v>2.203193E-3</v>
+      </c>
+      <c r="G47">
+        <v>3.4752060000000002E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>100</v>
+      </c>
+      <c r="B48">
+        <v>2.9079233999999999E-2</v>
+      </c>
+      <c r="C48">
+        <v>3.5235064000000003E-2</v>
+      </c>
+      <c r="D48">
+        <v>2.7568275E-2</v>
+      </c>
+      <c r="E48">
+        <v>2.7568275E-2</v>
+      </c>
+      <c r="F48">
+        <v>2.7568275E-2</v>
+      </c>
+      <c r="G48">
+        <v>2.2146722000000001E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>134</v>
+      </c>
+      <c r="B49">
+        <v>2.6635868E-2</v>
+      </c>
+      <c r="C49">
+        <v>2.4016636000000001E-2</v>
+      </c>
+      <c r="D49">
+        <v>2.6303199999999999E-2</v>
+      </c>
+      <c r="E49">
+        <v>2.6303199999999999E-2</v>
+      </c>
+      <c r="F49">
+        <v>2.6303199999999999E-2</v>
+      </c>
+      <c r="G49">
+        <v>2.6590330999999998E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>103</v>
+      </c>
+      <c r="B50">
+        <v>4.8381750000000001E-3</v>
+      </c>
+      <c r="C50">
+        <v>3.134721E-3</v>
+      </c>
+      <c r="D50">
+        <v>6.0068229999999997E-3</v>
+      </c>
+      <c r="E50">
+        <v>6.0068229999999997E-3</v>
+      </c>
+      <c r="F50">
+        <v>6.0068229999999997E-3</v>
+      </c>
+      <c r="G50">
+        <v>5.2267370000000004E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>135</v>
+      </c>
+      <c r="B51">
+        <v>1.8086189999999999E-2</v>
+      </c>
+      <c r="C51">
+        <v>1.4844968E-2</v>
+      </c>
+      <c r="D51">
+        <v>2.0355207E-2</v>
+      </c>
+      <c r="E51">
+        <v>2.0355207E-2</v>
+      </c>
+      <c r="F51">
+        <v>2.0355207E-2</v>
+      </c>
+      <c r="G51">
+        <v>3.3177876000000002E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>136</v>
+      </c>
+      <c r="B52">
+        <v>1.819864E-3</v>
+      </c>
+      <c r="C52">
+        <v>4.0746410000000004E-3</v>
+      </c>
+      <c r="D52">
+        <v>3.1206480000000002E-3</v>
+      </c>
+      <c r="E52">
+        <v>3.1206480000000002E-3</v>
+      </c>
+      <c r="F52">
+        <v>3.1206480000000002E-3</v>
+      </c>
+      <c r="G52">
+        <v>3.4206919999999999E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>137</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>138</v>
+      </c>
+      <c r="B54">
+        <v>0</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>139</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>140</v>
+      </c>
+      <c r="B56">
+        <v>0</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>141</v>
+      </c>
+      <c r="B57">
+        <v>0</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>142</v>
+      </c>
+      <c r="B58">
+        <v>0</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>143</v>
+      </c>
+      <c r="B59">
+        <v>0</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>144</v>
+      </c>
+      <c r="B60">
+        <v>0</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>145</v>
+      </c>
+      <c r="B61">
+        <v>0</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
         <v>0</v>
       </c>
     </row>
@@ -821,173 +3547,439 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
-    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D0F4B8D-70F0-48E9-8C0A-87C272523328}">
+  <sheetPr>
+    <tabColor theme="4" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B2" s="17">
+        <f>About!$A$23*About!$A$45+'EV Fees'!C53</f>
+        <v>802.46412827002996</v>
+      </c>
+      <c r="C2" s="17">
+        <f>$B2*About!$A$37</f>
+        <v>1604.9282565400599</v>
+      </c>
+      <c r="D2" s="7">
+        <v>0</v>
+      </c>
+      <c r="E2" s="7">
+        <v>0</v>
+      </c>
+      <c r="F2" s="7">
+        <v>0</v>
+      </c>
+      <c r="G2" s="17">
+        <f>$B2*About!$A$36</f>
+        <v>401.23206413501498</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B3" s="17">
+        <f>About!$A$23*About!$A$45</f>
+        <v>676.19399999999996</v>
+      </c>
+      <c r="C3" s="17">
+        <f>$B3*About!$A$37</f>
+        <v>1352.3879999999999</v>
+      </c>
+      <c r="D3" s="7">
+        <v>0</v>
+      </c>
+      <c r="E3" s="7">
+        <v>0</v>
+      </c>
+      <c r="F3" s="7">
+        <v>0</v>
+      </c>
+      <c r="G3" s="17">
+        <f>$B3*About!$A$36</f>
+        <v>338.09699999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4" s="17">
+        <f>About!$A$23*About!$A$45</f>
+        <v>676.19399999999996</v>
+      </c>
+      <c r="C4" s="17">
+        <f>$B4*About!$A$37</f>
+        <v>1352.3879999999999</v>
+      </c>
+      <c r="D4" s="7">
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <v>0</v>
+      </c>
+      <c r="G4" s="17">
+        <f>$B4*About!$A$36</f>
+        <v>338.09699999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" s="17">
+        <f>About!$A$23*About!$A$45</f>
+        <v>676.19399999999996</v>
+      </c>
+      <c r="C5" s="17">
+        <f>$B5*About!$A$37</f>
+        <v>1352.3879999999999</v>
+      </c>
+      <c r="D5" s="7">
+        <v>0</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0</v>
+      </c>
+      <c r="G5" s="17">
+        <f>$B5*About!$A$36</f>
+        <v>338.09699999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" s="17">
+        <f>About!$A$23*About!$A$45+'EV Fees'!D53</f>
+        <v>710.41338837199999</v>
+      </c>
+      <c r="C6" s="17">
+        <f>$B6*About!$A$37</f>
+        <v>1420.826776744</v>
+      </c>
+      <c r="D6" s="7">
+        <v>0</v>
+      </c>
+      <c r="E6" s="7">
+        <v>0</v>
+      </c>
+      <c r="F6" s="7">
+        <v>0</v>
+      </c>
+      <c r="G6" s="17">
+        <f>$B6*About!$A$36</f>
+        <v>355.20669418599999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B7" s="17">
+        <f>About!$A$23*About!$A$45</f>
+        <v>676.19399999999996</v>
+      </c>
+      <c r="C7" s="17">
+        <f>$B7*About!$A$37</f>
+        <v>1352.3879999999999</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="7">
+        <v>0</v>
+      </c>
+      <c r="G7" s="17">
+        <f>$B7*About!$A$36</f>
+        <v>338.09699999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B8" s="17">
+        <f>About!$A$23*About!$A$45</f>
+        <v>676.19399999999996</v>
+      </c>
+      <c r="C8" s="17">
+        <f>$B8*About!$A$37</f>
+        <v>1352.3879999999999</v>
+      </c>
+      <c r="D8" s="7">
+        <v>0</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0</v>
+      </c>
+      <c r="F8" s="7">
+        <v>0</v>
+      </c>
+      <c r="G8" s="17">
+        <f>$B8*About!$A$36</f>
+        <v>338.09699999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32C974C1-A27E-4939-B3A1-C02AFB5993F8}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DEA72DF-C5E6-488B-9DB3-5B17317C19E2}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{297D8F00-D632-4504-B6E1-49A8C6BB421E}"/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF46E20E-56CA-4645-AA1F-4323C4BE4968}">
+  <sheetPr>
+    <tabColor theme="4" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B2" s="17">
+        <f>About!$A$23*About!$A$45+'EV Fees'!C53</f>
+        <v>802.46412827002996</v>
+      </c>
+      <c r="C2" s="17">
+        <f>$B2*About!$A$37</f>
+        <v>1604.9282565400599</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B3" s="17">
+        <f>About!$A$23*About!$A$45</f>
+        <v>676.19399999999996</v>
+      </c>
+      <c r="C3" s="17">
+        <f>$B3*About!$A$37</f>
+        <v>1352.3879999999999</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4" s="17">
+        <f>About!$A$23*About!$A$45</f>
+        <v>676.19399999999996</v>
+      </c>
+      <c r="C4" s="17">
+        <f>$B4*About!$A$37</f>
+        <v>1352.3879999999999</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" s="17">
+        <f>About!$A$23*About!$A$45+'EV Fees'!D53</f>
+        <v>710.41338837199999</v>
+      </c>
+      <c r="C5" s="17">
+        <f>$B5*About!$A$37</f>
+        <v>1420.826776744</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" s="17">
+        <f>About!$A$23*About!$A$45</f>
+        <v>676.19399999999996</v>
+      </c>
+      <c r="C6" s="17">
+        <f>$B6*About!$A$37</f>
+        <v>1352.3879999999999</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B7" s="17">
+        <f>About!$A$23*About!$A$45</f>
+        <v>676.19399999999996</v>
+      </c>
+      <c r="C7" s="17">
+        <f>$B7*About!$A$37</f>
+        <v>1352.3879999999999</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B8" s="17">
+        <f>About!$A$23*About!$A$45</f>
+        <v>676.19399999999996</v>
+      </c>
+      <c r="C8" s="17">
+        <f>$B8*About!$A$37</f>
+        <v>1352.3879999999999</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>